--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:12</t>
+    <t xml:space="preserve">2026-09-09 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:06</t>
+    <t xml:space="preserve">2026-09-17 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:03</t>
+    <t xml:space="preserve">2026-09-23 12:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:32</t>
+    <t xml:space="preserve">2026-10-02 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:09</t>
+    <t xml:space="preserve">2026-10-05 10:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -622,7 +622,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1157574.62</v>
+        <v>1157574.63</v>
       </c>
     </row>
     <row r="6">
@@ -826,7 +826,7 @@
         <v>2024</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1046057.62</v>
+        <v>1046057.63</v>
       </c>
     </row>
     <row r="18">
@@ -860,7 +860,7 @@
         <v>2024</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1030397.62</v>
+        <v>1030397.63</v>
       </c>
     </row>
     <row r="20">
@@ -877,7 +877,7 @@
         <v>2024</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1027274.12</v>
+        <v>1027274.13</v>
       </c>
     </row>
     <row r="21">
